--- a/Fase 2/Evidencias Proyecto/Evidencias de Documentación/Planificación Inicial/Matriz de Responsabilidades (RACI) - TTDH Automation.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de Documentación/Planificación Inicial/Matriz de Responsabilidades (RACI) - TTDH Automation.xlsx
@@ -209,7 +209,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_1" displayName="Table_1" ref="A5:E21" headerRowCount="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_1" displayName="Table_1" ref="A5:E22" headerRowCount="0">
   <tableColumns count="5">
     <tableColumn id="1" name="Column1"/>
     <tableColumn id="2" name="Column2"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="67.13" customWidth="1" style="6" min="1" max="1"/>
@@ -637,22 +637,22 @@
     <row r="11" s="6">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>7. Recepción por correo y extracción de documentos (OCR/IA)</t>
+          <t>7. Configuración del entorno de desarrollo y datos simulados</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>R/A</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -664,7 +664,7 @@
     <row r="12" s="6">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>8. Implementación del ETL</t>
+          <t>8. Recepción por correo y extracción de documentos (OCR/IA)</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -684,14 +684,14 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>R</t>
         </is>
       </c>
     </row>
     <row r="13" s="6">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>9. Implementación de validaciones y reglas de negocio</t>
+          <t>9. Implementación del ETL</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -701,12 +701,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -718,7 +718,7 @@
     <row r="14" s="6">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>10. Comparación histórica y trazabilidad</t>
+          <t>10. Implementación de validaciones y reglas de negocio</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -728,12 +728,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -745,7 +745,7 @@
     <row r="15" s="6">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>11. Desarrollo de dashboard y monitoreo</t>
+          <t>11. Comparación histórica y trazabilidad</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -772,7 +772,7 @@
     <row r="16" s="6">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>12. Implementación de reportes</t>
+          <t>12. Desarrollo de dashboard y monitoreo</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="17" s="6">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>13. Implementación del componente de IA (detección de anomalías)</t>
+          <t>13. Implementación de reportes</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -814,19 +814,19 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="18" s="6">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>14. Integración de componentes</t>
+          <t>14. Implementación del componente de IA (detección de anomalías)</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -836,12 +836,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="19" s="6">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>15. Pruebas funcionales y de integración</t>
+          <t>15. Integración de componentes</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -863,12 +863,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -880,7 +880,7 @@
     <row r="20" s="6">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>16. Correcciones y documentación final</t>
+          <t>16. Pruebas funcionales y de integración</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -907,7 +907,7 @@
     <row r="21" s="6">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>17. Presentación y cierre del proyecto</t>
+          <t>17. Correcciones y documentación final</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -926,6 +926,33 @@
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" s="6">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>18. Presentación y cierre del proyecto</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -937,7 +964,7 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B5:E20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B5:E22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"R,A,C,I,R/A"</formula1>
     </dataValidation>
   </dataValidations>
